--- a/master/result/55_重生校园_逆袭少女之路/55_重生校园_逆袭少女之路.xlsx
+++ b/master/result/55_重生校园_逆袭少女之路/55_重生校园_逆袭少女之路.xlsx
@@ -397,478 +397,605 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D42"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>apartment</v>
       </c>
       <c r="B2" t="str">
-        <v>apartment</v>
+        <v>/əˈpɑːtmənt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>公寓</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>sophomore</v>
       </c>
       <c r="B3" t="str">
-        <v>sophomore</v>
+        <v>/sophomore/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>二年级学生</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>sit</v>
       </c>
       <c r="B4" t="str">
-        <v>sit</v>
+        <v>/sɪt/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>坐</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>text</v>
       </c>
       <c r="B5" t="str">
-        <v>text</v>
+        <v>/text/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>教科书</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>astronaut</v>
       </c>
       <c r="B6" t="str">
-        <v>astronaut</v>
+        <v>/astronaut/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>宇航员</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>vivid</v>
       </c>
       <c r="B7" t="str">
-        <v>vivid</v>
+        <v>/vivid/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>生动的</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>golden</v>
       </c>
       <c r="B8" t="str">
-        <v>golden</v>
+        <v>/golden/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>金色</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>testify</v>
       </c>
       <c r="B9" t="str">
-        <v>testify</v>
+        <v>/testify/</v>
       </c>
       <c r="C9" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>作证</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>sincere</v>
       </c>
       <c r="B10" t="str">
-        <v>sincere</v>
+        <v>/sincere/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>真诚的</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>income</v>
       </c>
       <c r="B11" t="str">
-        <v>income</v>
+        <v>/income/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>收入</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>grand</v>
       </c>
       <c r="B12" t="str">
-        <v>grand</v>
+        <v>/grand/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>盛大</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>aloud</v>
       </c>
       <c r="B13" t="str">
-        <v>aloud</v>
+        <v>/aloud/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>大声地</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>pedestrian</v>
       </c>
       <c r="B14" t="str">
-        <v>pedestrian</v>
+        <v>/pedestrian/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>行人</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>refresh</v>
       </c>
       <c r="B15" t="str">
-        <v>refresh</v>
+        <v>/refresh/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>振作</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>everyday</v>
       </c>
       <c r="B16" t="str">
-        <v>everyday</v>
+        <v>/everyday/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>日常的</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>chocolate</v>
       </c>
       <c r="B17" t="str">
-        <v>chocolate</v>
+        <v>/ˈtʃɒklət/</v>
       </c>
       <c r="C17" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D17" t="str">
         <v>巧克力</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>swear</v>
       </c>
       <c r="B18" t="str">
-        <v>swear</v>
+        <v>/sweə/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>发誓</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>outbreak</v>
       </c>
       <c r="B19" t="str">
-        <v>outbreak</v>
+        <v>/outbreak/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>爆发</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>suggest</v>
       </c>
       <c r="B20" t="str">
-        <v>suggest</v>
+        <v>/səˈdʒest/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>建议</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>outrage</v>
       </c>
       <c r="B21" t="str">
-        <v>outrage</v>
+        <v>/outrage/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>愤怒</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>calm</v>
       </c>
       <c r="B22" t="str">
-        <v>calm</v>
+        <v>/kɑːm/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>平静</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>gather</v>
       </c>
       <c r="B23" t="str">
-        <v>gather</v>
+        <v>/ˈɡæðə/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>聚集</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>romance</v>
       </c>
       <c r="B24" t="str">
-        <v>romance</v>
+        <v>/romance/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>浪漫</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>remains</v>
       </c>
       <c r="B25" t="str">
-        <v>remains</v>
+        <v>/remains/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>残余</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>yawn</v>
       </c>
       <c r="B26" t="str">
-        <v>yawn</v>
+        <v>/yawn/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>打呵欠</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>refreshment</v>
       </c>
       <c r="B27" t="str">
-        <v>refreshment</v>
+        <v>/refreshment/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>点心</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>wool</v>
       </c>
       <c r="B28" t="str">
-        <v>wool</v>
+        <v>/wool/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>羊毛</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>lantern</v>
       </c>
       <c r="B29" t="str">
-        <v>lantern</v>
+        <v>/lantern/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>灯笼</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>gap</v>
       </c>
       <c r="B30" t="str">
-        <v>gap</v>
+        <v>/gap/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>差距</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>range</v>
       </c>
       <c r="B31" t="str">
-        <v>range</v>
+        <v>/reɪndʒ/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>范围</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>arrival</v>
       </c>
       <c r="B32" t="str">
-        <v>arrival</v>
+        <v>/arrival/</v>
       </c>
       <c r="C32" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>到达</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>artery</v>
       </c>
       <c r="B33" t="str">
-        <v>artery</v>
+        <v>/artery/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>主干道</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>monthly</v>
       </c>
       <c r="B34" t="str">
-        <v>monthly</v>
+        <v>/monthly/</v>
       </c>
       <c r="C34" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D34" t="str">
         <v>月刊</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>compensation</v>
       </c>
       <c r="B35" t="str">
-        <v>compensation</v>
+        <v>/ˌkɒmpenˈseɪʃn/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>补偿</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>status</v>
       </c>
       <c r="B36" t="str">
-        <v>status</v>
+        <v>/status/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>地位</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>adapt</v>
       </c>
       <c r="B37" t="str">
-        <v>adapt</v>
+        <v>/əˈdæpt/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>适应</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>dull</v>
       </c>
       <c r="B38" t="str">
-        <v>dull</v>
+        <v>/dull/</v>
       </c>
       <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>迟钝的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>transform</v>
       </c>
       <c r="B39" t="str">
-        <v>transform</v>
+        <v>/transform/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>改变</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>inherent</v>
       </c>
       <c r="B40" t="str">
-        <v>inherent</v>
+        <v>/inherent/</v>
       </c>
       <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>固有的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>outlook</v>
       </c>
       <c r="B41" t="str">
-        <v>outlook</v>
+        <v>/outlook/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>展望</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>forget</v>
       </c>
       <c r="B42" t="str">
-        <v>forget</v>
+        <v>/fəˈɡet/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>忘记</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
   </ignoredErrors>
 </worksheet>
 </file>